--- a/website/examples/example_odk_nfc_tag_write.xlsx
+++ b/website/examples/example_odk_nfc_tag_write.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="Ra23823d2fcce49db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="Rdd3cce0519364a7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="R3fa9328afeca4e86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" r:id="R444e46e2c27f44a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" r:id="R0bcbade7a51941de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" r:id="Rf6be4217d0d845a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -497,7 +497,7 @@
         <x:v>field-list</x:v>
       </x:c>
       <x:c r="I6" s="11" t="str">
-        <x:v>com.example.researchos.EXECUTE_METHOD(method_id='nfc_tag_write',input_value=${write_value},input_record_type='text/plain',input_overwrite_policy=${overwrite_policy_input},input_expected_current_hash=${expected_current_hash_input},return_mode='flat')</x:v>
+        <x:v>com.example.methodmesh.EXECUTE_METHOD(method_id='nfc_tag_write',input_value=${write_value},input_record_type='text/plain',input_overwrite_policy=${overwrite_policy_input},input_expected_current_hash=${expected_current_hash_input},return_mode='flat')</x:v>
       </x:c>
       <x:c r="J6" s="11"/>
       <x:c r="K6" s="11"/>
@@ -507,10 +507,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>researchos_execution_id</x:v>
+        <x:v>methodmesh_execution_id</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>ResearchOS execution ID</x:v>
+        <x:v>MethodMesh execution ID</x:v>
       </x:c>
       <x:c r="D7" s="11"/>
       <x:c r="E7" s="11"/>
@@ -528,10 +528,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>researchos_method_id</x:v>
+        <x:v>methodmesh_method_id</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>ResearchOS method ID</x:v>
+        <x:v>MethodMesh method ID</x:v>
       </x:c>
       <x:c r="D8" s="11"/>
       <x:c r="E8" s="11"/>
@@ -549,10 +549,10 @@
         <x:v>text</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>researchos_status</x:v>
+        <x:v>methodmesh_status</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>ResearchOS status</x:v>
+        <x:v>MethodMesh status</x:v>
       </x:c>
       <x:c r="D9" s="11"/>
       <x:c r="E9" s="11"/>
